--- a/Form_Processing.xlsx
+++ b/Form_Processing.xlsx
@@ -411,7 +411,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>From - 15/07/2026       To - 20/08/2026</v>
+        <v>From - 15/07/2026       To - 21/08/2026</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>FORM6</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>FORM8</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>AC Form Total</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -708,13 +708,13 @@
         <v>FORM6</v>
       </c>
       <c r="D9">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>12</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -889,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -915,13 +915,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D12">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>12</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M12">
         <v>23</v>
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="R12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>3</v>
       </c>
       <c r="L14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1099,7 +1099,7 @@
         <v>226</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -1128,13 +1128,13 @@
         <v>FORM8</v>
       </c>
       <c r="D15">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -1193,13 +1193,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D16">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G16">
         <v>48</v>
@@ -1217,7 +1217,7 @@
         <v>16</v>
       </c>
       <c r="L16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M16">
         <v>11</v>
@@ -1235,7 +1235,7 @@
         <v>243</v>
       </c>
       <c r="R16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -1264,34 +1264,34 @@
         <v>FORM6</v>
       </c>
       <c r="D17">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>338</v>
+        <v>44</v>
       </c>
       <c r="L17">
-        <v>227</v>
+        <v>155</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -1306,7 +1306,7 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>101</v>
+        <v>451</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1406,28 +1406,28 @@
         <v>FORM8</v>
       </c>
       <c r="D19">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         <v>4</v>
       </c>
       <c r="R19">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -1471,34 +1471,34 @@
         <v>AC Form Total</v>
       </c>
       <c r="D20">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J20">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>339</v>
+        <v>44</v>
       </c>
       <c r="L20">
-        <v>266</v>
+        <v>194</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -1513,7 +1513,7 @@
         <v>1036</v>
       </c>
       <c r="R20">
-        <v>326</v>
+        <v>693</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -1542,7 +1542,7 @@
         <v>FORM6</v>
       </c>
       <c r="D21">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>7</v>
       </c>
       <c r="G21">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1560,17 +1560,17 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>6</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
       <c r="N21">
         <v>1</v>
       </c>
@@ -1581,10 +1581,10 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R21">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -1755,13 +1755,13 @@
         <v>FORM8</v>
       </c>
       <c r="D24">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1820,16 +1820,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D25">
-        <v>3336</v>
+        <v>3346</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G25">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1838,16 +1838,16 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K25">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L25">
         <v>55</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>2</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="R25">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>9</v>
       </c>
       <c r="G26">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1909,16 +1909,16 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K26">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L26">
         <v>2</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="R26">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>FORM7</v>
       </c>
       <c r="D27">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R27">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="W27">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
@@ -2033,13 +2033,13 @@
         <v>FORM8</v>
       </c>
       <c r="D28">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>16</v>
       </c>
       <c r="R28">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="W28">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="29">
@@ -2098,16 +2098,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D29">
-        <v>3386</v>
+        <v>3391</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G29">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2116,16 +2116,16 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K29">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="L29">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -2137,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R29">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="W29">
-        <v>1970</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="30">
@@ -2169,16 +2169,16 @@
         <v>FORM6</v>
       </c>
       <c r="D30">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K30">
         <v>127</v>
@@ -2382,13 +2382,13 @@
         <v>FORM8</v>
       </c>
       <c r="D33">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2447,16 +2447,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D34">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G34">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K34">
         <v>130</v>
@@ -2518,16 +2518,16 @@
         <v>FORM6</v>
       </c>
       <c r="D35">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L35">
         <v>83</v>
@@ -2560,7 +2560,7 @@
         <v>32</v>
       </c>
       <c r="R35">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -2731,7 +2731,7 @@
         <v>FORM8</v>
       </c>
       <c r="D38">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L38">
         <v>2</v>
@@ -2796,16 +2796,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D39">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>133</v>
       </c>
       <c r="R39">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -2867,7 +2867,7 @@
         <v>FORM6</v>
       </c>
       <c r="D40">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>10</v>
       </c>
       <c r="G40">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H40">
         <v>2</v>
@@ -3009,13 +3009,13 @@
         <v>FORM8</v>
       </c>
       <c r="D42">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -3074,16 +3074,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D43">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G43">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H43">
         <v>2</v>
@@ -3287,13 +3287,13 @@
         <v>FORM8</v>
       </c>
       <c r="D46">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G46">
         <v>42</v>
@@ -3352,13 +3352,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D47">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G47">
         <v>52</v>
@@ -3423,13 +3423,13 @@
         <v>FORM6</v>
       </c>
       <c r="D48">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G48">
         <v>88</v>
@@ -3565,13 +3565,13 @@
         <v>FORM8</v>
       </c>
       <c r="D50">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G50">
         <v>12</v>
@@ -3630,13 +3630,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D51">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G51">
         <v>100</v>
@@ -3701,7 +3701,7 @@
         <v>FORM6</v>
       </c>
       <c r="D52">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3719,16 +3719,16 @@
         <v>25</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>670</v>
+        <v>578</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N52">
         <v>0</v>
@@ -3740,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -3914,13 +3914,13 @@
         <v>FORM8</v>
       </c>
       <c r="D55">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>218</v>
+        <v>102</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -3953,10 +3953,10 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R55">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -3979,13 +3979,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D56">
-        <v>1597</v>
+        <v>1608</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G56">
         <v>22</v>
@@ -3997,16 +3997,16 @@
         <v>33</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>888</v>
+        <v>680</v>
       </c>
       <c r="L56">
         <v>95</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -4018,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="R56">
-        <v>63</v>
+        <v>269</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -4328,37 +4328,37 @@
         <v>FORM6</v>
       </c>
       <c r="D61">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G61">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="K61">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -4367,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R61">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         <v>FORM8</v>
       </c>
       <c r="D64">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G64">
         <v>130</v>
@@ -4606,37 +4606,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D65">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G65">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
       <c r="I65">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J65">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="K65">
-        <v>589</v>
+        <v>529</v>
       </c>
       <c r="L65">
         <v>36</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -4645,10 +4645,10 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="R65">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -4686,7 +4686,7 @@
         <v>3</v>
       </c>
       <c r="G66">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -4695,10 +4695,10 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K66">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="R66">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -4819,13 +4819,13 @@
         <v>FORM8</v>
       </c>
       <c r="D68">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G68">
         <v>11</v>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -4861,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -4884,16 +4884,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D69">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G69">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -4902,10 +4902,10 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K69">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="L69">
         <v>33</v>
@@ -4926,7 +4926,7 @@
         <v>118</v>
       </c>
       <c r="R69">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -4955,16 +4955,16 @@
         <v>FORM6</v>
       </c>
       <c r="D70">
-        <v>2864</v>
+        <v>2867</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G70">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -4973,16 +4973,16 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="K70">
-        <v>2289</v>
+        <v>2188</v>
       </c>
       <c r="L70">
         <v>4</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R70">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -5097,16 +5097,16 @@
         <v>FORM8</v>
       </c>
       <c r="D72">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G72">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -5115,7 +5115,7 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K72">
         <v>647</v>
@@ -5139,7 +5139,7 @@
         <v>1</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -5162,16 +5162,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D73">
-        <v>3908</v>
+        <v>3916</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G73">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -5180,16 +5180,16 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="K73">
-        <v>2975</v>
+        <v>2874</v>
       </c>
       <c r="L73">
         <v>79</v>
       </c>
       <c r="M73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N73">
         <v>2</v>
@@ -5201,10 +5201,10 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R73">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -5233,28 +5233,28 @@
         <v>FORM6</v>
       </c>
       <c r="D74">
-        <v>3094</v>
+        <v>3140</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="G74">
-        <v>718</v>
+        <v>453</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J74">
-        <v>1902</v>
+        <v>2195</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L74">
         <v>13</v>
@@ -5375,13 +5375,13 @@
         <v>FORM8</v>
       </c>
       <c r="D76">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>882</v>
+        <v>612</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -5390,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -5440,28 +5440,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D77">
-        <v>5474</v>
+        <v>5529</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>1323</v>
+        <v>1064</v>
       </c>
       <c r="G77">
-        <v>718</v>
+        <v>453</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
       <c r="I77">
-        <v>2</v>
+        <v>284</v>
       </c>
       <c r="J77">
-        <v>1902</v>
+        <v>2195</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L77">
         <v>1178</v>
@@ -5511,13 +5511,13 @@
         <v>FORM6</v>
       </c>
       <c r="D78">
-        <v>4114</v>
+        <v>4146</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="G78">
         <v>591</v>
@@ -5526,22 +5526,22 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="J78">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="K78">
         <v>771</v>
       </c>
       <c r="L78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78">
         <v>0</v>
       </c>
       <c r="N78">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="O78">
         <v>2</v>
@@ -5553,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="R78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>FORM8</v>
       </c>
       <c r="D81">
-        <v>716</v>
+        <v>733</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="G81">
         <v>2</v>
@@ -5739,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -5789,13 +5789,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D82">
-        <v>5783</v>
+        <v>5832</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>1043</v>
+        <v>1087</v>
       </c>
       <c r="G82">
         <v>593</v>
@@ -5804,22 +5804,22 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>697</v>
+        <v>767</v>
       </c>
       <c r="J82">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="K82">
         <v>771</v>
       </c>
       <c r="L82">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="M82">
         <v>0</v>
       </c>
       <c r="N82">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="O82">
         <v>2</v>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -5860,40 +5860,40 @@
         <v>FORM6</v>
       </c>
       <c r="D83">
-        <v>8744</v>
+        <v>8828</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="F83">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G83">
-        <v>1631</v>
+        <v>1703</v>
       </c>
       <c r="H83">
         <v>0</v>
       </c>
       <c r="I83">
-        <v>1310</v>
+        <v>565</v>
       </c>
       <c r="J83">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="K83">
-        <v>4770</v>
+        <v>4923</v>
       </c>
       <c r="L83">
         <v>439</v>
       </c>
       <c r="M83">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="N83">
-        <v>33</v>
+        <v>786</v>
       </c>
       <c r="O83">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P83">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>48</v>
       </c>
       <c r="R83">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -5940,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
         <v>3</v>
-      </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-      <c r="I84">
-        <v>1</v>
-      </c>
-      <c r="J84">
-        <v>2</v>
       </c>
       <c r="K84">
         <v>3</v>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>4</v>
@@ -6017,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -6073,31 +6073,31 @@
         <v>FORM8</v>
       </c>
       <c r="D86">
-        <v>2143</v>
+        <v>2159</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="G86">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H86">
         <v>0</v>
       </c>
       <c r="I86">
-        <v>903</v>
+        <v>808</v>
       </c>
       <c r="J86">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K86">
         <v>27</v>
       </c>
       <c r="L86">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M86">
         <v>14</v>
@@ -6112,10 +6112,10 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R86">
-        <v>1048</v>
+        <v>1129</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -6138,49 +6138,49 @@
         <v>AC Form Total</v>
       </c>
       <c r="D87">
-        <v>11935</v>
+        <v>12035</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="G87">
-        <v>1651</v>
+        <v>1720</v>
       </c>
       <c r="H87">
         <v>0</v>
       </c>
       <c r="I87">
-        <v>2214</v>
+        <v>1386</v>
       </c>
       <c r="J87">
-        <v>189</v>
+        <v>90</v>
       </c>
       <c r="K87">
-        <v>4805</v>
+        <v>4958</v>
       </c>
       <c r="L87">
-        <v>694</v>
+        <v>707</v>
       </c>
       <c r="M87">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N87">
-        <v>34</v>
+        <v>787</v>
       </c>
       <c r="O87">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="P87">
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="R87">
-        <v>1089</v>
+        <v>1171</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -6209,40 +6209,40 @@
         <v>FORM6</v>
       </c>
       <c r="D88">
-        <v>4674</v>
+        <v>4645</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
       <c r="F88">
-        <v>511</v>
+        <v>431</v>
       </c>
       <c r="G88">
-        <v>1112</v>
+        <v>1054</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88">
-        <v>515</v>
+        <v>469</v>
       </c>
       <c r="J88">
-        <v>749</v>
+        <v>807</v>
       </c>
       <c r="K88">
         <v>781</v>
       </c>
       <c r="L88">
-        <v>723</v>
+        <v>991</v>
       </c>
       <c r="M88">
         <v>27</v>
       </c>
       <c r="N88">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="P88">
         <v>0</v>
@@ -6351,13 +6351,13 @@
         <v>FORM7</v>
       </c>
       <c r="D90">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -6422,13 +6422,13 @@
         <v>FORM8</v>
       </c>
       <c r="D91">
-        <v>1068</v>
+        <v>1131</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -6487,40 +6487,40 @@
         <v>AC Form Total</v>
       </c>
       <c r="D92">
-        <v>7852</v>
+        <v>7887</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>1573</v>
+        <v>1502</v>
       </c>
       <c r="G92">
-        <v>1114</v>
+        <v>1056</v>
       </c>
       <c r="H92">
         <v>0</v>
       </c>
       <c r="I92">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="J92">
-        <v>749</v>
+        <v>807</v>
       </c>
       <c r="K92">
         <v>782</v>
       </c>
       <c r="L92">
-        <v>2055</v>
+        <v>2323</v>
       </c>
       <c r="M92">
         <v>27</v>
       </c>
       <c r="N92">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="O92">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="P92">
         <v>0</v>
@@ -6558,13 +6558,13 @@
         <v>FORM6</v>
       </c>
       <c r="D93">
-        <v>3909</v>
+        <v>3930</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G93">
         <v>31</v>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -6591,7 +6591,7 @@
         <v>185</v>
       </c>
       <c r="O93">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D97">
-        <v>6106</v>
+        <v>6127</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G97">
         <v>31</v>
@@ -6851,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="J97">
         <v>1</v>
@@ -6869,7 +6869,7 @@
         <v>185</v>
       </c>
       <c r="O97">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="P97">
         <v>0</v>
@@ -6907,49 +6907,49 @@
         <v>FORM6</v>
       </c>
       <c r="D98">
-        <v>3187</v>
+        <v>3221</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G98">
-        <v>1204</v>
+        <v>1178</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J98">
-        <v>1100</v>
+        <v>170</v>
       </c>
       <c r="K98">
-        <v>2</v>
+        <v>814</v>
       </c>
       <c r="L98">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="M98">
         <v>25</v>
       </c>
       <c r="N98">
+        <v>14</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
         <v>3</v>
       </c>
-      <c r="O98">
-        <v>8</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>1</v>
-      </c>
       <c r="R98">
-        <v>44</v>
+        <v>209</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -7120,13 +7120,13 @@
         <v>FORM8</v>
       </c>
       <c r="D101">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -7185,49 +7185,49 @@
         <v>AC Form Total</v>
       </c>
       <c r="D102">
-        <v>4934</v>
+        <v>4978</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
       <c r="F102">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="G102">
-        <v>1206</v>
+        <v>1180</v>
       </c>
       <c r="H102">
         <v>0</v>
       </c>
       <c r="I102">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="J102">
-        <v>1102</v>
+        <v>172</v>
       </c>
       <c r="K102">
-        <v>2</v>
+        <v>814</v>
       </c>
       <c r="L102">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="M102">
         <v>25</v>
       </c>
       <c r="N102">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="O102">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P102">
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="R102">
-        <v>551</v>
+        <v>716</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -7256,46 +7256,46 @@
         <v>FORM6</v>
       </c>
       <c r="D103">
-        <v>4662</v>
+        <v>4695</v>
       </c>
       <c r="E103">
         <v>0</v>
       </c>
       <c r="F103">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G103">
-        <v>574</v>
+        <v>302</v>
       </c>
       <c r="H103">
         <v>0</v>
       </c>
       <c r="I103">
-        <v>369</v>
+        <v>464</v>
       </c>
       <c r="J103">
-        <v>101</v>
+        <v>384</v>
       </c>
       <c r="K103">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="L103">
         <v>554</v>
       </c>
       <c r="M103">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N103">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="O103">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P103">
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R103">
         <v>8</v>
@@ -7469,13 +7469,13 @@
         <v>FORM8</v>
       </c>
       <c r="D106">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
       <c r="F106">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G106">
         <v>19</v>
@@ -7534,46 +7534,46 @@
         <v>AC Form Total</v>
       </c>
       <c r="D107">
-        <v>7066</v>
+        <v>7105</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="G107">
-        <v>621</v>
+        <v>349</v>
       </c>
       <c r="H107">
         <v>0</v>
       </c>
       <c r="I107">
-        <v>782</v>
+        <v>877</v>
       </c>
       <c r="J107">
-        <v>118</v>
+        <v>401</v>
       </c>
       <c r="K107">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="L107">
         <v>1373</v>
       </c>
       <c r="M107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N107">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="O107">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P107">
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R107">
         <v>373</v>
@@ -7605,16 +7605,16 @@
         <v>FORM6</v>
       </c>
       <c r="D108">
-        <v>4482</v>
+        <v>4528</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="G108">
-        <v>2507</v>
+        <v>2456</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>5</v>
       </c>
       <c r="J108">
-        <v>981</v>
+        <v>1006</v>
       </c>
       <c r="K108">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -7635,10 +7635,10 @@
         <v>0</v>
       </c>
       <c r="N108">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="O108">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -7818,28 +7818,28 @@
         <v>FORM8</v>
       </c>
       <c r="D111">
-        <v>1803</v>
+        <v>1890</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>246</v>
+        <v>97</v>
       </c>
       <c r="G111">
-        <v>597</v>
+        <v>780</v>
       </c>
       <c r="H111">
         <v>0</v>
       </c>
       <c r="I111">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J111">
-        <v>909</v>
+        <v>485</v>
       </c>
       <c r="K111">
-        <v>1</v>
+        <v>470</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -7883,28 +7883,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D112">
-        <v>7702</v>
+        <v>7835</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>438</v>
+        <v>327</v>
       </c>
       <c r="G112">
-        <v>3128</v>
+        <v>3260</v>
       </c>
       <c r="H112">
         <v>0</v>
       </c>
       <c r="I112">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J112">
-        <v>1890</v>
+        <v>1491</v>
       </c>
       <c r="K112">
-        <v>999</v>
+        <v>1483</v>
       </c>
       <c r="L112">
         <v>469</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="N112">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="O112">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -7954,28 +7954,28 @@
         <v>FORM6</v>
       </c>
       <c r="D113">
-        <v>3921</v>
+        <v>4152</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>890</v>
+        <v>831</v>
       </c>
       <c r="G113">
-        <v>1824</v>
+        <v>2042</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J113">
-        <v>302</v>
+        <v>25</v>
       </c>
       <c r="K113">
-        <v>786</v>
+        <v>1110</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -7984,7 +7984,7 @@
         <v>7</v>
       </c>
       <c r="N113">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="O113">
         <v>34</v>
@@ -8167,13 +8167,13 @@
         <v>FORM8</v>
       </c>
       <c r="D116">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>401</v>
+        <v>251</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -8182,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>582</v>
+        <v>737</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -8209,7 +8209,7 @@
         <v>24</v>
       </c>
       <c r="R116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -8232,28 +8232,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D117">
-        <v>6155</v>
+        <v>6392</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>1313</v>
+        <v>1104</v>
       </c>
       <c r="G117">
-        <v>1824</v>
+        <v>2042</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
       <c r="I117">
-        <v>586</v>
+        <v>745</v>
       </c>
       <c r="J117">
-        <v>302</v>
+        <v>25</v>
       </c>
       <c r="K117">
-        <v>788</v>
+        <v>1112</v>
       </c>
       <c r="L117">
         <v>410</v>
@@ -8262,7 +8262,7 @@
         <v>7</v>
       </c>
       <c r="N117">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="O117">
         <v>34</v>
@@ -8274,7 +8274,7 @@
         <v>698</v>
       </c>
       <c r="R117">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -8303,16 +8303,16 @@
         <v>FORM6</v>
       </c>
       <c r="D118">
-        <v>5235</v>
+        <v>5362</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G118">
-        <v>2378</v>
+        <v>1971</v>
       </c>
       <c r="H118">
         <v>5</v>
@@ -8321,10 +8321,10 @@
         <v>4</v>
       </c>
       <c r="J118">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="K118">
-        <v>2591</v>
+        <v>3102</v>
       </c>
       <c r="L118">
         <v>0</v>
@@ -8333,10 +8333,10 @@
         <v>0</v>
       </c>
       <c r="N118">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O118">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -8383,7 +8383,7 @@
         <v>11</v>
       </c>
       <c r="G119">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -8392,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K119">
         <v>270</v>
@@ -8445,16 +8445,16 @@
         <v>FORM8</v>
       </c>
       <c r="D120">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G120">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>56</v>
       </c>
       <c r="J120">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K120">
         <v>447</v>
@@ -8510,16 +8510,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D121">
-        <v>6304</v>
+        <v>6435</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="G121">
-        <v>2518</v>
+        <v>2082</v>
       </c>
       <c r="H121">
         <v>5</v>
@@ -8528,10 +8528,10 @@
         <v>60</v>
       </c>
       <c r="J121">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K121">
-        <v>3308</v>
+        <v>3819</v>
       </c>
       <c r="L121">
         <v>0</v>
@@ -8540,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="N121">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O121">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -8581,28 +8581,28 @@
         <v>FORM6</v>
       </c>
       <c r="D122">
-        <v>3846</v>
+        <v>4038</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>605</v>
+        <v>567</v>
       </c>
       <c r="G122">
-        <v>530</v>
+        <v>28</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
       <c r="I122">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J122">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K122">
-        <v>2370</v>
+        <v>3014</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -8611,10 +8611,10 @@
         <v>0</v>
       </c>
       <c r="N122">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O122">
-        <v>178</v>
+        <v>291</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -8741,10 +8741,10 @@
         <v>0</v>
       </c>
       <c r="J124">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K124">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="L124">
         <v>1924</v>
@@ -8794,16 +8794,16 @@
         <v>FORM8</v>
       </c>
       <c r="D125">
-        <v>1282</v>
+        <v>1293</v>
       </c>
       <c r="E125">
         <v>0</v>
       </c>
       <c r="F125">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="G125">
-        <v>232</v>
+        <v>44</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -8812,10 +8812,10 @@
         <v>53</v>
       </c>
       <c r="J125">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="K125">
-        <v>744</v>
+        <v>1058</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -8859,28 +8859,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D126">
-        <v>7310</v>
+        <v>7513</v>
       </c>
       <c r="E126">
         <v>0</v>
       </c>
       <c r="F126">
-        <v>780</v>
+        <v>707</v>
       </c>
       <c r="G126">
-        <v>937</v>
+        <v>247</v>
       </c>
       <c r="H126">
         <v>0</v>
       </c>
       <c r="I126">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="J126">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c r="K126">
-        <v>3148</v>
+        <v>4130</v>
       </c>
       <c r="L126">
         <v>1924</v>
@@ -8889,10 +8889,10 @@
         <v>0</v>
       </c>
       <c r="N126">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O126">
-        <v>185</v>
+        <v>298</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -8930,28 +8930,28 @@
         <v>FORM6</v>
       </c>
       <c r="D127">
-        <v>1708</v>
+        <v>1568</v>
       </c>
       <c r="E127">
         <v>0</v>
       </c>
       <c r="F127">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G127">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H127">
         <v>0</v>
       </c>
       <c r="I127">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="J127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127">
-        <v>1458</v>
+        <v>1463</v>
       </c>
       <c r="L127">
         <v>0</v>
@@ -8960,10 +8960,10 @@
         <v>0</v>
       </c>
       <c r="N127">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>FORM7</v>
       </c>
       <c r="D128">
-        <v>2343</v>
+        <v>2370</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -9010,7 +9010,7 @@
         <v>17</v>
       </c>
       <c r="G128">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -9022,10 +9022,10 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>1540</v>
+        <v>774</v>
       </c>
       <c r="L128">
-        <v>247</v>
+        <v>1041</v>
       </c>
       <c r="M128">
         <v>0</v>
@@ -9072,13 +9072,13 @@
         <v>FORM8</v>
       </c>
       <c r="D129">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G129">
         <v>27</v>
@@ -9090,10 +9090,10 @@
         <v>19</v>
       </c>
       <c r="J129">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>596</v>
+        <v>695</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -9137,40 +9137,40 @@
         <v>AC Form Total</v>
       </c>
       <c r="D130">
-        <v>4841</v>
+        <v>4734</v>
       </c>
       <c r="E130">
         <v>0</v>
       </c>
       <c r="F130">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G130">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="H130">
         <v>0</v>
       </c>
       <c r="I130">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="J130">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K130">
-        <v>3594</v>
+        <v>2932</v>
       </c>
       <c r="L130">
-        <v>247</v>
+        <v>1041</v>
       </c>
       <c r="M130">
         <v>0</v>
       </c>
       <c r="N130">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -9208,28 +9208,28 @@
         <v>FORM6</v>
       </c>
       <c r="D131">
-        <v>1407</v>
+        <v>1398</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G131">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="H131">
         <v>0</v>
       </c>
       <c r="I131">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J131">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K131">
-        <v>312</v>
+        <v>200</v>
       </c>
       <c r="L131">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>137</v>
       </c>
       <c r="N131">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="O131">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -9250,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="R131">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -9350,16 +9350,16 @@
         <v>FORM8</v>
       </c>
       <c r="D133">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G133">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -9371,7 +9371,7 @@
         <v>9</v>
       </c>
       <c r="K133">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -9392,7 +9392,7 @@
         <v>15</v>
       </c>
       <c r="R133">
-        <v>557</v>
+        <v>591</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -9415,28 +9415,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D134">
-        <v>2635</v>
+        <v>2631</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G134">
-        <v>946</v>
+        <v>968</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J134">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K134">
-        <v>354</v>
+        <v>215</v>
       </c>
       <c r="L134">
         <v>30</v>
@@ -9445,10 +9445,10 @@
         <v>137</v>
       </c>
       <c r="N134">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="O134">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -9457,7 +9457,7 @@
         <v>429</v>
       </c>
       <c r="R134">
-        <v>558</v>
+        <v>706</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -9486,16 +9486,16 @@
         <v>FORM6</v>
       </c>
       <c r="D135">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G135">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -9504,19 +9504,19 @@
         <v>0</v>
       </c>
       <c r="J135">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N135">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -9628,7 +9628,7 @@
         <v>FORM7</v>
       </c>
       <c r="D137">
-        <v>4166</v>
+        <v>4204</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -9637,7 +9637,7 @@
         <v>15</v>
       </c>
       <c r="G137">
-        <v>3735</v>
+        <v>3499</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -9646,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>402</v>
+        <v>676</v>
       </c>
       <c r="K137">
         <v>1</v>
@@ -9699,16 +9699,16 @@
         <v>FORM8</v>
       </c>
       <c r="D138">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G138">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>1</v>
       </c>
       <c r="J138">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="K138">
         <v>4</v>
@@ -9764,16 +9764,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D139">
-        <v>5835</v>
+        <v>5908</v>
       </c>
       <c r="E139">
         <v>0</v>
       </c>
       <c r="F139">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G139">
-        <v>4599</v>
+        <v>4332</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -9782,19 +9782,19 @@
         <v>1</v>
       </c>
       <c r="J139">
-        <v>979</v>
+        <v>1305</v>
       </c>
       <c r="K139">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N139">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -9835,16 +9835,16 @@
         <v>FORM6</v>
       </c>
       <c r="D140">
-        <v>1897</v>
+        <v>1920</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
       <c r="F140">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G140">
-        <v>881</v>
+        <v>907</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -9853,7 +9853,7 @@
         <v>2</v>
       </c>
       <c r="J140">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="K140">
         <v>41</v>
@@ -9868,7 +9868,7 @@
         <v>92</v>
       </c>
       <c r="O140">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P140">
         <v>0</v>
@@ -9977,16 +9977,16 @@
         <v>FORM8</v>
       </c>
       <c r="D142">
-        <v>979</v>
+        <v>988</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G142">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -9995,7 +9995,7 @@
         <v>43</v>
       </c>
       <c r="J142">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="K142">
         <v>18</v>
@@ -10042,16 +10042,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D143">
-        <v>4577</v>
+        <v>4609</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G143">
-        <v>2897</v>
+        <v>2913</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -10060,7 +10060,7 @@
         <v>45</v>
       </c>
       <c r="J143">
-        <v>979</v>
+        <v>998</v>
       </c>
       <c r="K143">
         <v>59</v>
@@ -10075,7 +10075,7 @@
         <v>101</v>
       </c>
       <c r="O143">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P143">
         <v>0</v>
@@ -10113,16 +10113,16 @@
         <v>FORM6</v>
       </c>
       <c r="D144">
-        <v>2246</v>
+        <v>2268</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="F144">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G144">
-        <v>667</v>
+        <v>642</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -10131,7 +10131,7 @@
         <v>61</v>
       </c>
       <c r="J144">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="K144">
         <v>1245</v>
@@ -10143,10 +10143,10 @@
         <v>0</v>
       </c>
       <c r="N144">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O144">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P144">
         <v>0</v>
@@ -10273,13 +10273,13 @@
         <v>0</v>
       </c>
       <c r="J146">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="K146">
         <v>45</v>
       </c>
       <c r="L146">
-        <v>764</v>
+        <v>926</v>
       </c>
       <c r="M146">
         <v>0</v>
@@ -10326,16 +10326,16 @@
         <v>FORM8</v>
       </c>
       <c r="D147">
-        <v>1267</v>
+        <v>1274</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G147">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H147">
         <v>1</v>
@@ -10344,7 +10344,7 @@
         <v>14</v>
       </c>
       <c r="J147">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K147">
         <v>172</v>
@@ -10391,16 +10391,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D148">
-        <v>4735</v>
+        <v>4764</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="G148">
-        <v>790</v>
+        <v>761</v>
       </c>
       <c r="H148">
         <v>2</v>
@@ -10409,22 +10409,22 @@
         <v>75</v>
       </c>
       <c r="J148">
-        <v>351</v>
+        <v>218</v>
       </c>
       <c r="K148">
         <v>1462</v>
       </c>
       <c r="L148">
-        <v>764</v>
+        <v>926</v>
       </c>
       <c r="M148">
         <v>0</v>
       </c>
       <c r="N148">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="O148">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P148">
         <v>0</v>
@@ -10462,13 +10462,13 @@
         <v>FORM6</v>
       </c>
       <c r="D149">
-        <v>2164</v>
+        <v>2178</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="G149">
         <v>7</v>
@@ -10477,16 +10477,16 @@
         <v>0</v>
       </c>
       <c r="I149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149">
         <v>4</v>
       </c>
       <c r="K149">
-        <v>282</v>
+        <v>161</v>
       </c>
       <c r="L149">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M149">
         <v>0</v>
@@ -10495,16 +10495,16 @@
         <v>0</v>
       </c>
       <c r="O149">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P149">
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -10628,7 +10628,7 @@
         <v>1</v>
       </c>
       <c r="L151">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M151">
         <v>0</v>
@@ -10646,7 +10646,7 @@
         <v>890</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -10675,13 +10675,13 @@
         <v>FORM8</v>
       </c>
       <c r="D152">
-        <v>1044</v>
+        <v>1056</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -10696,7 +10696,7 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>43</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="S152">
         <v>0</v>
@@ -10740,13 +10740,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D153">
-        <v>4368</v>
+        <v>4394</v>
       </c>
       <c r="E153">
         <v>0</v>
       </c>
       <c r="F153">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="G153">
         <v>7</v>
@@ -10755,16 +10755,16 @@
         <v>0</v>
       </c>
       <c r="I153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J153">
         <v>4</v>
       </c>
       <c r="K153">
-        <v>336</v>
+        <v>174</v>
       </c>
       <c r="L153">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="M153">
         <v>0</v>
@@ -10773,16 +10773,16 @@
         <v>0</v>
       </c>
       <c r="O153">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P153">
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="S153">
         <v>0</v>
@@ -10811,16 +10811,16 @@
         <v>FORM6</v>
       </c>
       <c r="D154">
-        <v>1987</v>
+        <v>2106</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
       <c r="F154">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G154">
-        <v>1522</v>
+        <v>1512</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -10829,10 +10829,10 @@
         <v>11</v>
       </c>
       <c r="J154">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -10841,16 +10841,16 @@
         <v>0</v>
       </c>
       <c r="N154">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="O154">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P154">
         <v>0</v>
       </c>
       <c r="Q154">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="R154">
         <v>0</v>
@@ -10891,7 +10891,7 @@
         <v>13</v>
       </c>
       <c r="G155">
-        <v>1061</v>
+        <v>355</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -10903,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>501</v>
+        <v>1207</v>
       </c>
       <c r="L155">
         <v>184</v>
@@ -10953,16 +10953,16 @@
         <v>FORM8</v>
       </c>
       <c r="D156">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G156">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -10971,10 +10971,10 @@
         <v>8</v>
       </c>
       <c r="J156">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="K156">
-        <v>259</v>
+        <v>177</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -10992,10 +10992,10 @@
         <v>0</v>
       </c>
       <c r="Q156">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="R156">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="S156">
         <v>0</v>
@@ -11018,16 +11018,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D157">
-        <v>4723</v>
+        <v>4853</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="G157">
-        <v>2753</v>
+        <v>1922</v>
       </c>
       <c r="H157">
         <v>1</v>
@@ -11036,10 +11036,10 @@
         <v>19</v>
       </c>
       <c r="J157">
-        <v>646</v>
+        <v>741</v>
       </c>
       <c r="K157">
-        <v>760</v>
+        <v>1523</v>
       </c>
       <c r="L157">
         <v>184</v>
@@ -11048,19 +11048,19 @@
         <v>0</v>
       </c>
       <c r="N157">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="O157">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P157">
         <v>0</v>
       </c>
       <c r="Q157">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="R157">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="S157">
         <v>0</v>
@@ -11089,16 +11089,16 @@
         <v>FORM6</v>
       </c>
       <c r="D158">
-        <v>1795</v>
+        <v>1807</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
       <c r="F158">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G158">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -11107,7 +11107,7 @@
         <v>37</v>
       </c>
       <c r="J158">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K158">
         <v>0</v>
@@ -11122,7 +11122,7 @@
         <v>47</v>
       </c>
       <c r="O158">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P158">
         <v>0</v>
@@ -11231,13 +11231,13 @@
         <v>FORM8</v>
       </c>
       <c r="D160">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G160">
         <v>32</v>
@@ -11296,16 +11296,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D161">
-        <v>2688</v>
+        <v>2709</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="G161">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -11314,7 +11314,7 @@
         <v>56</v>
       </c>
       <c r="J161">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K161">
         <v>0</v>
@@ -11329,7 +11329,7 @@
         <v>47</v>
       </c>
       <c r="O161">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P161">
         <v>0</v>
@@ -11367,16 +11367,16 @@
         <v>FORM6</v>
       </c>
       <c r="D162">
-        <v>1970</v>
+        <v>1991</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
       <c r="F162">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="G162">
-        <v>682</v>
+        <v>359</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -11385,7 +11385,7 @@
         <v>2</v>
       </c>
       <c r="J162">
-        <v>680</v>
+        <v>1003</v>
       </c>
       <c r="K162">
         <v>2</v>
@@ -11400,7 +11400,7 @@
         <v>24</v>
       </c>
       <c r="O162">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="P162">
         <v>0</v>
@@ -11438,7 +11438,7 @@
         <v>FORM7</v>
       </c>
       <c r="D163">
-        <v>1904</v>
+        <v>1912</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -11459,10 +11459,10 @@
         <v>1</v>
       </c>
       <c r="K163">
-        <v>1180</v>
+        <v>236</v>
       </c>
       <c r="L163">
-        <v>715</v>
+        <v>1667</v>
       </c>
       <c r="M163">
         <v>0</v>
@@ -11509,13 +11509,13 @@
         <v>FORM8</v>
       </c>
       <c r="D164">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -11574,16 +11574,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D165">
-        <v>4664</v>
+        <v>4699</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="G165">
-        <v>689</v>
+        <v>366</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -11592,13 +11592,13 @@
         <v>24</v>
       </c>
       <c r="J165">
-        <v>1426</v>
+        <v>1749</v>
       </c>
       <c r="K165">
-        <v>1182</v>
+        <v>238</v>
       </c>
       <c r="L165">
-        <v>715</v>
+        <v>1667</v>
       </c>
       <c r="M165">
         <v>1</v>
@@ -11607,7 +11607,7 @@
         <v>24</v>
       </c>
       <c r="O165">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="P165">
         <v>0</v>
@@ -11645,16 +11645,16 @@
         <v>FORM6</v>
       </c>
       <c r="D166">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G166">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -11663,16 +11663,16 @@
         <v>0</v>
       </c>
       <c r="J166">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="K166">
-        <v>121</v>
+        <v>349</v>
       </c>
       <c r="L166">
         <v>0</v>
       </c>
       <c r="M166">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N166">
         <v>0</v>
@@ -11787,13 +11787,13 @@
         <v>FORM8</v>
       </c>
       <c r="D168">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
       <c r="F168">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -11805,10 +11805,10 @@
         <v>2</v>
       </c>
       <c r="J168">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K168">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -11852,16 +11852,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D169">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="E169">
         <v>0</v>
       </c>
       <c r="F169">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G169">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -11870,16 +11870,16 @@
         <v>2</v>
       </c>
       <c r="J169">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K169">
-        <v>225</v>
+        <v>456</v>
       </c>
       <c r="L169">
         <v>218</v>
       </c>
       <c r="M169">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N169">
         <v>0</v>
@@ -11923,16 +11923,16 @@
         <v>FORM6</v>
       </c>
       <c r="D170">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E170">
         <v>0</v>
       </c>
       <c r="F170">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G170">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -11941,7 +11941,7 @@
         <v>0</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K170">
         <v>315</v>
@@ -11953,7 +11953,7 @@
         <v>1</v>
       </c>
       <c r="N170">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -12065,7 +12065,7 @@
         <v>FORM8</v>
       </c>
       <c r="D172">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -12074,13 +12074,13 @@
         <v>18</v>
       </c>
       <c r="G172">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J172">
         <v>1</v>
@@ -12095,7 +12095,7 @@
         <v>0</v>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O172">
         <v>0</v>
@@ -12104,7 +12104,7 @@
         <v>0</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172">
         <v>13</v>
@@ -12130,25 +12130,25 @@
         <v>AC Form Total</v>
       </c>
       <c r="D173">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G173">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J173">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K173">
         <v>439</v>
@@ -12160,7 +12160,7 @@
         <v>1</v>
       </c>
       <c r="N173">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -12169,7 +12169,7 @@
         <v>0</v>
       </c>
       <c r="Q173">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R173">
         <v>63</v>
@@ -12201,46 +12201,46 @@
         <v>FORM6</v>
       </c>
       <c r="D174">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G174">
-        <v>411</v>
+        <v>301</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J174">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="K174">
-        <v>158</v>
+        <v>261</v>
       </c>
       <c r="L174">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M174">
         <v>64</v>
       </c>
       <c r="N174">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O174">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P174">
         <v>0</v>
       </c>
       <c r="Q174">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R174">
         <v>85</v>
@@ -12293,10 +12293,10 @@
         <v>0</v>
       </c>
       <c r="K175">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L175">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M175">
         <v>0</v>
@@ -12343,16 +12343,16 @@
         <v>FORM8</v>
       </c>
       <c r="D176">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E176">
         <v>0</v>
       </c>
       <c r="F176">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G176">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -12361,7 +12361,7 @@
         <v>7</v>
       </c>
       <c r="J176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K176">
         <v>5</v>
@@ -12408,46 +12408,46 @@
         <v>AC Form Total</v>
       </c>
       <c r="D177">
-        <v>3181</v>
+        <v>3189</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G177">
-        <v>475</v>
+        <v>364</v>
       </c>
       <c r="H177">
         <v>0</v>
       </c>
       <c r="I177">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="J177">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="K177">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="L177">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M177">
         <v>64</v>
       </c>
       <c r="N177">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="O177">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P177">
         <v>0</v>
       </c>
       <c r="Q177">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="R177">
         <v>93</v>
@@ -12479,13 +12479,13 @@
         <v>FORM6</v>
       </c>
       <c r="D178">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E178">
         <v>0</v>
       </c>
       <c r="F178">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G178">
         <v>74</v>
@@ -12497,7 +12497,7 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K178">
         <v>77</v>
@@ -12506,7 +12506,7 @@
         <v>0</v>
       </c>
       <c r="M178">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N178">
         <v>2</v>
@@ -12621,16 +12621,16 @@
         <v>FORM8</v>
       </c>
       <c r="D180">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E180">
         <v>0</v>
       </c>
       <c r="F180">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G180">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -12639,7 +12639,7 @@
         <v>0</v>
       </c>
       <c r="J180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K180">
         <v>9</v>
@@ -12686,16 +12686,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D181">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="E181">
         <v>0</v>
       </c>
       <c r="F181">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G181">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -12704,7 +12704,7 @@
         <v>0</v>
       </c>
       <c r="J181">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K181">
         <v>215</v>
@@ -12713,7 +12713,7 @@
         <v>0</v>
       </c>
       <c r="M181">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N181">
         <v>2</v>
@@ -12757,16 +12757,16 @@
         <v>FORM6</v>
       </c>
       <c r="D182">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="E182">
         <v>0</v>
       </c>
       <c r="F182">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G182">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -12775,16 +12775,16 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="K182">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="L182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M182">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N182">
         <v>28</v>
@@ -12799,7 +12799,7 @@
         <v>3</v>
       </c>
       <c r="R182">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -12849,13 +12849,13 @@
         <v>6</v>
       </c>
       <c r="K183">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L183">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N183">
         <v>0</v>
@@ -12964,16 +12964,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D185">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="E185">
         <v>0</v>
       </c>
       <c r="F185">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G185">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -12982,16 +12982,16 @@
         <v>3</v>
       </c>
       <c r="J185">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="K185">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="L185">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M185">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="N185">
         <v>36</v>
@@ -13006,7 +13006,7 @@
         <v>224</v>
       </c>
       <c r="R185">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -13035,16 +13035,16 @@
         <v>FORM6</v>
       </c>
       <c r="D186">
-        <v>2505</v>
+        <v>2512</v>
       </c>
       <c r="E186">
         <v>0</v>
       </c>
       <c r="F186">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G186">
-        <v>735</v>
+        <v>671</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -13053,19 +13053,19 @@
         <v>11</v>
       </c>
       <c r="J186">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="K186">
-        <v>1413</v>
+        <v>1298</v>
       </c>
       <c r="L186">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M186">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="N186">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="O186">
         <v>5</v>
@@ -13074,10 +13074,10 @@
         <v>0</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R186">
-        <v>51</v>
+        <v>280</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -13177,7 +13177,7 @@
         <v>FORM7</v>
       </c>
       <c r="D188">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -13195,10 +13195,10 @@
         <v>0</v>
       </c>
       <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
         <v>10</v>
-      </c>
-      <c r="K188">
-        <v>0</v>
       </c>
       <c r="L188">
         <v>287</v>
@@ -13234,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="W188">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189">
@@ -13248,16 +13248,16 @@
         <v>FORM8</v>
       </c>
       <c r="D189">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E189">
         <v>0</v>
       </c>
       <c r="F189">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G189">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -13266,19 +13266,19 @@
         <v>14</v>
       </c>
       <c r="J189">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K189">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="L189">
         <v>0</v>
       </c>
       <c r="M189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N189">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O189">
         <v>0</v>
@@ -13290,7 +13290,7 @@
         <v>1</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -13313,16 +13313,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D190">
-        <v>3795</v>
+        <v>3815</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G190">
-        <v>796</v>
+        <v>727</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -13331,19 +13331,19 @@
         <v>25</v>
       </c>
       <c r="J190">
-        <v>262</v>
+        <v>138</v>
       </c>
       <c r="K190">
-        <v>2029</v>
+        <v>1918</v>
       </c>
       <c r="L190">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M190">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N190">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="O190">
         <v>5</v>
@@ -13352,10 +13352,10 @@
         <v>0</v>
       </c>
       <c r="Q190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R190">
-        <v>51</v>
+        <v>293</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -13370,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="W190">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191">
@@ -13384,16 +13384,16 @@
         <v>FORM6</v>
       </c>
       <c r="D191">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="E191">
         <v>0</v>
       </c>
       <c r="F191">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G191">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H191">
         <v>0</v>
@@ -13402,22 +13402,22 @@
         <v>0</v>
       </c>
       <c r="J191">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K191">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="L191">
         <v>20</v>
       </c>
       <c r="M191">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N191">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P191">
         <v>0</v>
@@ -13426,7 +13426,7 @@
         <v>18</v>
       </c>
       <c r="R191">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -13455,13 +13455,13 @@
         <v>FORM7</v>
       </c>
       <c r="D192">
-        <v>755</v>
+        <v>833</v>
       </c>
       <c r="E192">
         <v>0</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192">
         <v>2</v>
@@ -13512,7 +13512,7 @@
         <v>0</v>
       </c>
       <c r="W192">
-        <v>591</v>
+        <v>668</v>
       </c>
     </row>
     <row r="193">
@@ -13526,13 +13526,13 @@
         <v>FORM8</v>
       </c>
       <c r="D193">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E193">
         <v>0</v>
       </c>
       <c r="F193">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G193">
         <v>10</v>
@@ -13591,16 +13591,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D194">
-        <v>2159</v>
+        <v>2244</v>
       </c>
       <c r="E194">
         <v>0</v>
       </c>
       <c r="F194">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G194">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H194">
         <v>0</v>
@@ -13609,22 +13609,22 @@
         <v>2</v>
       </c>
       <c r="J194">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K194">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L194">
         <v>108</v>
       </c>
       <c r="M194">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N194">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P194">
         <v>0</v>
@@ -13633,7 +13633,7 @@
         <v>102</v>
       </c>
       <c r="R194">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="W194">
-        <v>1309</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="195">
@@ -13662,16 +13662,16 @@
         <v>FORM6</v>
       </c>
       <c r="D195">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="E195">
         <v>0</v>
       </c>
       <c r="F195">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G195">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="H195">
         <v>1</v>
@@ -13680,22 +13680,22 @@
         <v>0</v>
       </c>
       <c r="J195">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="K195">
-        <v>829</v>
+        <v>855</v>
       </c>
       <c r="L195">
         <v>29</v>
       </c>
       <c r="M195">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N195">
         <v>10</v>
       </c>
       <c r="O195">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P195">
         <v>0</v>
@@ -13704,7 +13704,7 @@
         <v>6</v>
       </c>
       <c r="R195">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -13804,16 +13804,16 @@
         <v>FORM8</v>
       </c>
       <c r="D197">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E197">
         <v>0</v>
       </c>
       <c r="F197">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G197">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="H197">
         <v>0</v>
@@ -13822,10 +13822,10 @@
         <v>7</v>
       </c>
       <c r="J197">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="K197">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -13837,7 +13837,7 @@
         <v>4</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P197">
         <v>0</v>
@@ -13869,16 +13869,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D198">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G198">
-        <v>319</v>
+        <v>133</v>
       </c>
       <c r="H198">
         <v>1</v>
@@ -13887,22 +13887,22 @@
         <v>7</v>
       </c>
       <c r="J198">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="K198">
-        <v>967</v>
+        <v>1003</v>
       </c>
       <c r="L198">
         <v>49</v>
       </c>
       <c r="M198">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N198">
         <v>14</v>
       </c>
       <c r="O198">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P198">
         <v>0</v>
@@ -13911,7 +13911,7 @@
         <v>17</v>
       </c>
       <c r="R198">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S198">
         <v>0</v>
@@ -13940,19 +13940,19 @@
         <v>FORM6</v>
       </c>
       <c r="D199">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="E199">
         <v>0</v>
       </c>
       <c r="F199">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H199">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -13961,16 +13961,16 @@
         <v>0</v>
       </c>
       <c r="K199">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L199">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="M199">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O199">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R199">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="S199">
         <v>0</v>
@@ -14088,10 +14088,10 @@
         <v>0</v>
       </c>
       <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
         <v>11</v>
-      </c>
-      <c r="G201">
-        <v>0</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -14106,7 +14106,7 @@
         <v>25</v>
       </c>
       <c r="L201">
-        <v>318</v>
+        <v>262</v>
       </c>
       <c r="M201">
         <v>0</v>
@@ -14121,7 +14121,7 @@
         <v>0</v>
       </c>
       <c r="Q201">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -14153,28 +14153,28 @@
         <v>FORM8</v>
       </c>
       <c r="D202">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E202">
         <v>0</v>
       </c>
       <c r="F202">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="G202">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I202">
         <v>12</v>
       </c>
       <c r="J202">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K202">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L202">
         <v>1</v>
@@ -14183,7 +14183,7 @@
         <v>7</v>
       </c>
       <c r="N202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O202">
         <v>0</v>
@@ -14192,7 +14192,7 @@
         <v>0</v>
       </c>
       <c r="Q202">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -14218,37 +14218,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D203">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="E203">
         <v>0</v>
       </c>
       <c r="F203">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="G203">
-        <v>252</v>
+        <v>321</v>
       </c>
       <c r="H203">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I203">
         <v>12</v>
       </c>
       <c r="J203">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K203">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="L203">
-        <v>395</v>
+        <v>310</v>
       </c>
       <c r="M203">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N203">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O203">
         <v>0</v>
@@ -14257,10 +14257,10 @@
         <v>0</v>
       </c>
       <c r="Q203">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="R203">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="S203">
         <v>1</v>
@@ -14289,16 +14289,16 @@
         <v>FORM6</v>
       </c>
       <c r="D204">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="E204">
         <v>0</v>
       </c>
       <c r="F204">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -14307,22 +14307,22 @@
         <v>0</v>
       </c>
       <c r="J204">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K204">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="L204">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M204">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="N204">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P204">
         <v>0</v>
@@ -14331,7 +14331,7 @@
         <v>0</v>
       </c>
       <c r="R204">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -14431,16 +14431,16 @@
         <v>FORM8</v>
       </c>
       <c r="D206">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E206">
         <v>0</v>
       </c>
       <c r="F206">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G206">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H206">
         <v>0</v>
@@ -14473,7 +14473,7 @@
         <v>4</v>
       </c>
       <c r="R206">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="S206">
         <v>0</v>
@@ -14496,16 +14496,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D207">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="E207">
         <v>0</v>
       </c>
       <c r="F207">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G207">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -14514,22 +14514,22 @@
         <v>7</v>
       </c>
       <c r="J207">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K207">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="L207">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="M207">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="N207">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P207">
         <v>0</v>
@@ -14538,7 +14538,7 @@
         <v>17</v>
       </c>
       <c r="R207">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -14576,7 +14576,7 @@
         <v>95</v>
       </c>
       <c r="G208">
-        <v>1555</v>
+        <v>1423</v>
       </c>
       <c r="H208">
         <v>1</v>
@@ -14585,19 +14585,19 @@
         <v>0</v>
       </c>
       <c r="J208">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="K208">
-        <v>510</v>
+        <v>284</v>
       </c>
       <c r="L208">
         <v>71</v>
       </c>
       <c r="M208">
-        <v>294</v>
+        <v>442</v>
       </c>
       <c r="N208">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O208">
         <v>0</v>
@@ -14606,19 +14606,19 @@
         <v>0</v>
       </c>
       <c r="Q208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R208">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T208">
         <v>0</v>
       </c>
       <c r="U208">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V208">
         <v>0</v>
@@ -14638,13 +14638,13 @@
         <v>FORM7</v>
       </c>
       <c r="D209">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E209">
         <v>0</v>
       </c>
       <c r="F209">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -14709,13 +14709,13 @@
         <v>FORM8</v>
       </c>
       <c r="D210">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E210">
         <v>0</v>
       </c>
       <c r="F210">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G210">
         <v>92</v>
@@ -14727,10 +14727,10 @@
         <v>6</v>
       </c>
       <c r="J210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -14751,7 +14751,7 @@
         <v>2</v>
       </c>
       <c r="R210">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -14774,16 +14774,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D211">
-        <v>3745</v>
+        <v>3747</v>
       </c>
       <c r="E211">
         <v>0</v>
       </c>
       <c r="F211">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G211">
-        <v>1647</v>
+        <v>1515</v>
       </c>
       <c r="H211">
         <v>1</v>
@@ -14792,19 +14792,19 @@
         <v>6</v>
       </c>
       <c r="J211">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="K211">
-        <v>624</v>
+        <v>387</v>
       </c>
       <c r="L211">
         <v>194</v>
       </c>
       <c r="M211">
-        <v>302</v>
+        <v>450</v>
       </c>
       <c r="N211">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -14813,19 +14813,19 @@
         <v>0</v>
       </c>
       <c r="Q211">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R211">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T211">
         <v>0</v>
       </c>
       <c r="U211">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V211">
         <v>0</v>
@@ -14845,16 +14845,16 @@
         <v>FORM6</v>
       </c>
       <c r="D212">
-        <v>2295</v>
+        <v>2299</v>
       </c>
       <c r="E212">
         <v>0</v>
       </c>
       <c r="F212">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G212">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H212">
         <v>0</v>
@@ -14863,10 +14863,10 @@
         <v>0</v>
       </c>
       <c r="J212">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K212">
-        <v>1624</v>
+        <v>1334</v>
       </c>
       <c r="L212">
         <v>0</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="R212">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -14993,7 +14993,7 @@
         <v>0</v>
       </c>
       <c r="F214">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="K214">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L214">
         <v>0</v>
@@ -15029,7 +15029,7 @@
         <v>0</v>
       </c>
       <c r="R214">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -15052,16 +15052,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D215">
-        <v>3461</v>
+        <v>3465</v>
       </c>
       <c r="E215">
         <v>0</v>
       </c>
       <c r="F215">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G215">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H215">
         <v>0</v>
@@ -15070,10 +15070,10 @@
         <v>13</v>
       </c>
       <c r="J215">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K215">
-        <v>1642</v>
+        <v>1346</v>
       </c>
       <c r="L215">
         <v>132</v>
@@ -15094,7 +15094,7 @@
         <v>151</v>
       </c>
       <c r="R215">
-        <v>590</v>
+        <v>895</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -15123,7 +15123,7 @@
         <v>FORM6</v>
       </c>
       <c r="D216">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -15132,7 +15132,7 @@
         <v>9</v>
       </c>
       <c r="G216">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H216">
         <v>0</v>
@@ -15265,13 +15265,13 @@
         <v>FORM8</v>
       </c>
       <c r="D218">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E218">
         <v>0</v>
       </c>
       <c r="F218">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G218">
         <v>1</v>
@@ -15330,16 +15330,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D219">
-        <v>1795</v>
+        <v>1798</v>
       </c>
       <c r="E219">
         <v>0</v>
       </c>
       <c r="F219">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G219">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H219">
         <v>0</v>
@@ -15401,16 +15401,16 @@
         <v>FORM6</v>
       </c>
       <c r="D220">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="E220">
         <v>0</v>
       </c>
       <c r="F220">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G220">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H220">
         <v>0</v>
@@ -15419,22 +15419,22 @@
         <v>2</v>
       </c>
       <c r="J220">
-        <v>340</v>
+        <v>2</v>
       </c>
       <c r="K220">
-        <v>236</v>
+        <v>174</v>
       </c>
       <c r="L220">
         <v>0</v>
       </c>
       <c r="M220">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="N220">
         <v>57</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P220">
         <v>0</v>
@@ -15443,7 +15443,7 @@
         <v>56</v>
       </c>
       <c r="R220">
-        <v>335</v>
+        <v>670</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -15552,7 +15552,7 @@
         <v>0</v>
       </c>
       <c r="G222">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H222">
         <v>0</v>
@@ -15561,7 +15561,7 @@
         <v>0</v>
       </c>
       <c r="J222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K222">
         <v>47</v>
@@ -15614,16 +15614,16 @@
         <v>FORM8</v>
       </c>
       <c r="D223">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E223">
         <v>0</v>
       </c>
       <c r="F223">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G223">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="H223">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="J223">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="K223">
-        <v>225</v>
+        <v>57</v>
       </c>
       <c r="L223">
         <v>0</v>
@@ -15656,7 +15656,7 @@
         <v>2</v>
       </c>
       <c r="R223">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -15679,16 +15679,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D224">
-        <v>1792</v>
+        <v>1810</v>
       </c>
       <c r="E224">
         <v>0</v>
       </c>
       <c r="F224">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G224">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="H224">
         <v>0</v>
@@ -15697,22 +15697,22 @@
         <v>2</v>
       </c>
       <c r="J224">
-        <v>342</v>
+        <v>51</v>
       </c>
       <c r="K224">
-        <v>508</v>
+        <v>278</v>
       </c>
       <c r="L224">
         <v>67</v>
       </c>
       <c r="M224">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="N224">
         <v>59</v>
       </c>
       <c r="O224">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P224">
         <v>0</v>
@@ -15721,7 +15721,7 @@
         <v>152</v>
       </c>
       <c r="R224">
-        <v>356</v>
+        <v>869</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -15750,7 +15750,7 @@
         <v>FORM6</v>
       </c>
       <c r="D225">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -15759,7 +15759,7 @@
         <v>6</v>
       </c>
       <c r="G225">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="J225">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="K225">
         <v>107</v>
@@ -15783,7 +15783,7 @@
         <v>9</v>
       </c>
       <c r="O225">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P225">
         <v>0</v>
@@ -15892,7 +15892,7 @@
         <v>FORM7</v>
       </c>
       <c r="D227">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -15907,7 +15907,7 @@
         <v>0</v>
       </c>
       <c r="I227">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="J227">
         <v>0</v>
@@ -15931,10 +15931,10 @@
         <v>0</v>
       </c>
       <c r="Q227">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -15949,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="W227">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="228">
@@ -15963,16 +15963,16 @@
         <v>FORM8</v>
       </c>
       <c r="D228">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E228">
         <v>0</v>
       </c>
       <c r="F228">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G228">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -15981,7 +15981,7 @@
         <v>12</v>
       </c>
       <c r="J228">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="K228">
         <v>13</v>
@@ -16028,25 +16028,25 @@
         <v>AC Form Total</v>
       </c>
       <c r="D229">
-        <v>2315</v>
+        <v>2327</v>
       </c>
       <c r="E229">
         <v>0</v>
       </c>
       <c r="F229">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G229">
-        <v>403</v>
+        <v>284</v>
       </c>
       <c r="H229">
         <v>0</v>
       </c>
       <c r="I229">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="J229">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="K229">
         <v>126</v>
@@ -16061,16 +16061,16 @@
         <v>9</v>
       </c>
       <c r="O229">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P229">
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="R229">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -16085,7 +16085,7 @@
         <v>0</v>
       </c>
       <c r="W229">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="230">
@@ -16099,13 +16099,13 @@
         <v>FORM6</v>
       </c>
       <c r="D230">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E230">
         <v>0</v>
       </c>
       <c r="F230">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G230">
         <v>95</v>
@@ -16123,7 +16123,7 @@
         <v>16</v>
       </c>
       <c r="L230">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M230">
         <v>0</v>
@@ -16141,7 +16141,7 @@
         <v>1</v>
       </c>
       <c r="R230">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="S230">
         <v>0</v>
@@ -16194,7 +16194,7 @@
         <v>0</v>
       </c>
       <c r="L231">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M231">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>147</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S231">
         <v>0</v>
@@ -16241,13 +16241,13 @@
         <v>FORM8</v>
       </c>
       <c r="D232">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E232">
         <v>0</v>
       </c>
       <c r="F232">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G232">
         <v>2</v>
@@ -16306,13 +16306,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D233">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="E233">
         <v>0</v>
       </c>
       <c r="F233">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G233">
         <v>99</v>
@@ -16330,7 +16330,7 @@
         <v>18</v>
       </c>
       <c r="L233">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M233">
         <v>1</v>
@@ -16348,7 +16348,7 @@
         <v>162</v>
       </c>
       <c r="R233">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="S233">
         <v>0</v>
@@ -16377,16 +16377,16 @@
         <v>FORM6</v>
       </c>
       <c r="D234">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="E234">
         <v>0</v>
       </c>
       <c r="F234">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G234">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -16395,19 +16395,19 @@
         <v>0</v>
       </c>
       <c r="J234">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K234">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L234">
         <v>0</v>
       </c>
       <c r="M234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O234">
         <v>0</v>
@@ -16419,7 +16419,7 @@
         <v>6</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S234">
         <v>0</v>
@@ -16519,7 +16519,7 @@
         <v>FORM7</v>
       </c>
       <c r="D236">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -16537,10 +16537,10 @@
         <v>0</v>
       </c>
       <c r="J236">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K236">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L236">
         <v>26</v>
@@ -16576,7 +16576,7 @@
         <v>0</v>
       </c>
       <c r="W236">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="237">
@@ -16590,13 +16590,13 @@
         <v>FORM8</v>
       </c>
       <c r="D237">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E237">
         <v>0</v>
       </c>
       <c r="F237">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G237">
         <v>0</v>
@@ -16608,10 +16608,10 @@
         <v>1</v>
       </c>
       <c r="J237">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K237">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="L237">
         <v>0</v>
@@ -16632,7 +16632,7 @@
         <v>28</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S237">
         <v>0</v>
@@ -16655,16 +16655,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D238">
-        <v>2155</v>
+        <v>2166</v>
       </c>
       <c r="E238">
         <v>0</v>
       </c>
       <c r="F238">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G238">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -16673,19 +16673,19 @@
         <v>1</v>
       </c>
       <c r="J238">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K238">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="L238">
         <v>28</v>
       </c>
       <c r="M238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O238">
         <v>0</v>
@@ -16697,7 +16697,7 @@
         <v>158</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -16712,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="W238">
-        <v>841</v>
+        <v>849</v>
       </c>
     </row>
     <row r="239">
@@ -16747,7 +16747,7 @@
         <v>215</v>
       </c>
       <c r="K239">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="L239">
         <v>3</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="R239">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -16797,7 +16797,7 @@
         <v>FORM7</v>
       </c>
       <c r="D240">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -16854,7 +16854,7 @@
         <v>0</v>
       </c>
       <c r="W240">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -16868,13 +16868,13 @@
         <v>FORM8</v>
       </c>
       <c r="D241">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E241">
         <v>0</v>
       </c>
       <c r="F241">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G241">
         <v>0</v>
@@ -16933,13 +16933,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D242">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="E242">
         <v>0</v>
       </c>
       <c r="F242">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G242">
         <v>108</v>
@@ -16954,7 +16954,7 @@
         <v>222</v>
       </c>
       <c r="K242">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="L242">
         <v>22</v>
@@ -16975,7 +16975,7 @@
         <v>148</v>
       </c>
       <c r="R242">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -16990,7 +16990,7 @@
         <v>0</v>
       </c>
       <c r="W242">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="243">
@@ -17004,7 +17004,7 @@
         <v>FORM6</v>
       </c>
       <c r="D243">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -17013,7 +17013,7 @@
         <v>1</v>
       </c>
       <c r="G243">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -17075,7 +17075,7 @@
         <v>FORM7</v>
       </c>
       <c r="D244">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -17132,7 +17132,7 @@
         <v>0</v>
       </c>
       <c r="W244">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="245">
@@ -17146,13 +17146,13 @@
         <v>FORM8</v>
       </c>
       <c r="D245">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E245">
         <v>0</v>
       </c>
       <c r="F245">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G245">
         <v>0</v>
@@ -17179,7 +17179,7 @@
         <v>3</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P245">
         <v>0</v>
@@ -17211,16 +17211,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D246">
-        <v>2703</v>
+        <v>2738</v>
       </c>
       <c r="E246">
         <v>0</v>
       </c>
       <c r="F246">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G246">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H246">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>3</v>
       </c>
       <c r="O246">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P246">
         <v>0</v>
@@ -17268,7 +17268,7 @@
         <v>0</v>
       </c>
       <c r="W246">
-        <v>465</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247">
@@ -17282,37 +17282,37 @@
         <v>FORM6</v>
       </c>
       <c r="D247">
-        <v>1626</v>
+        <v>1635</v>
       </c>
       <c r="E247">
         <v>0</v>
       </c>
       <c r="F247">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G247">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H247">
         <v>1</v>
       </c>
       <c r="I247">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J247">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K247">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="L247">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M247">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N247">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="O247">
         <v>0</v>
@@ -17324,7 +17324,7 @@
         <v>11</v>
       </c>
       <c r="R247">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -17353,7 +17353,7 @@
         <v>FORM7</v>
       </c>
       <c r="D248">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -17377,7 +17377,7 @@
         <v>0</v>
       </c>
       <c r="L248">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M248">
         <v>0</v>
@@ -17395,7 +17395,7 @@
         <v>219</v>
       </c>
       <c r="R248">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -17410,7 +17410,7 @@
         <v>0</v>
       </c>
       <c r="W248">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="249">
@@ -17424,13 +17424,13 @@
         <v>FORM8</v>
       </c>
       <c r="D249">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E249">
         <v>0</v>
       </c>
       <c r="F249">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G249">
         <v>0</v>
@@ -17439,19 +17439,19 @@
         <v>0</v>
       </c>
       <c r="I249">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J249">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K249">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="L249">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N249">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="Q249">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R249">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="S249">
         <v>0</v>
@@ -17481,7 +17481,7 @@
         <v>0</v>
       </c>
       <c r="W249">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="250">
@@ -17489,37 +17489,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D250">
-        <v>2769</v>
+        <v>2788</v>
       </c>
       <c r="E250">
         <v>0</v>
       </c>
       <c r="F250">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="G250">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H250">
         <v>1</v>
       </c>
       <c r="I250">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J250">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="K250">
-        <v>398</v>
+        <v>277</v>
       </c>
       <c r="L250">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="M250">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N250">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="O250">
         <v>0</v>
@@ -17528,10 +17528,10 @@
         <v>0</v>
       </c>
       <c r="Q250">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="R250">
-        <v>123</v>
+        <v>241</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -17546,7 +17546,7 @@
         <v>0</v>
       </c>
       <c r="W250">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="251">
@@ -17560,16 +17560,16 @@
         <v>FORM6</v>
       </c>
       <c r="D251">
-        <v>1713</v>
+        <v>1748</v>
       </c>
       <c r="E251">
         <v>0</v>
       </c>
       <c r="F251">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="G251">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -17578,7 +17578,7 @@
         <v>0</v>
       </c>
       <c r="J251">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K251">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         <v>2</v>
       </c>
       <c r="M251">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="N251">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O251">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P251">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>FORM7</v>
       </c>
       <c r="D252">
-        <v>723</v>
+        <v>758</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -17688,7 +17688,7 @@
         <v>0</v>
       </c>
       <c r="W252">
-        <v>96</v>
+        <v>131</v>
       </c>
     </row>
     <row r="253">
@@ -17702,13 +17702,13 @@
         <v>FORM8</v>
       </c>
       <c r="D253">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="E253">
         <v>0</v>
       </c>
       <c r="F253">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G253">
         <v>44</v>
@@ -17767,16 +17767,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D254">
-        <v>3140</v>
+        <v>3218</v>
       </c>
       <c r="E254">
         <v>0</v>
       </c>
       <c r="F254">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="G254">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H254">
         <v>1</v>
@@ -17785,7 +17785,7 @@
         <v>1</v>
       </c>
       <c r="J254">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K254">
         <v>93</v>
@@ -17794,13 +17794,13 @@
         <v>23</v>
       </c>
       <c r="M254">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="N254">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O254">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P254">
         <v>0</v>
@@ -17824,7 +17824,7 @@
         <v>0</v>
       </c>
       <c r="W254">
-        <v>1716</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="255">
@@ -17838,16 +17838,16 @@
         <v>FORM6</v>
       </c>
       <c r="D255">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E255">
         <v>0</v>
       </c>
       <c r="F255">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G255">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -17856,23 +17856,23 @@
         <v>0</v>
       </c>
       <c r="J255">
+        <v>1</v>
+      </c>
+      <c r="K255">
+        <v>310</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>50</v>
+      </c>
+      <c r="N255">
+        <v>5</v>
+      </c>
+      <c r="O255">
         <v>2</v>
       </c>
-      <c r="K255">
-        <v>312</v>
-      </c>
-      <c r="L255">
-        <v>0</v>
-      </c>
-      <c r="M255">
-        <v>45</v>
-      </c>
-      <c r="N255">
-        <v>3</v>
-      </c>
-      <c r="O255">
-        <v>0</v>
-      </c>
       <c r="P255">
         <v>0</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>0</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S255">
         <v>0</v>
@@ -17918,7 +17918,7 @@
         <v>0</v>
       </c>
       <c r="G256">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -17927,7 +17927,7 @@
         <v>0</v>
       </c>
       <c r="J256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K256">
         <v>11</v>
@@ -17980,40 +17980,40 @@
         <v>FORM8</v>
       </c>
       <c r="D257">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E257">
         <v>0</v>
       </c>
       <c r="F257">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G257">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H257">
         <v>0</v>
       </c>
       <c r="I257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J257">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K257">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L257">
         <v>2</v>
       </c>
       <c r="M257">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N257">
         <v>0</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P257">
         <v>0</v>
@@ -18045,28 +18045,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D258">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="E258">
         <v>0</v>
       </c>
       <c r="F258">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G258">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="H258">
         <v>0</v>
       </c>
       <c r="I258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J258">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K258">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="L258">
         <v>7</v>
@@ -18075,10 +18075,10 @@
         <v>99</v>
       </c>
       <c r="N258">
+        <v>5</v>
+      </c>
+      <c r="O258">
         <v>3</v>
-      </c>
-      <c r="O258">
-        <v>0</v>
       </c>
       <c r="P258">
         <v>0</v>
@@ -18087,7 +18087,7 @@
         <v>94</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S258">
         <v>0</v>
@@ -18116,40 +18116,40 @@
         <v>FORM6</v>
       </c>
       <c r="D259">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E259">
         <v>0</v>
       </c>
       <c r="F259">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G259">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="H259">
         <v>0</v>
       </c>
       <c r="I259">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J259">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K259">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="L259">
         <v>0</v>
       </c>
       <c r="M259">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N259">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P259">
         <v>0</v>
@@ -18258,7 +18258,7 @@
         <v>FORM7</v>
       </c>
       <c r="D261">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -18276,13 +18276,13 @@
         <v>0</v>
       </c>
       <c r="J261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K261">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L261">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M261">
         <v>0</v>
@@ -18300,7 +18300,7 @@
         <v>212</v>
       </c>
       <c r="R261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S261">
         <v>0</v>
@@ -18315,7 +18315,7 @@
         <v>0</v>
       </c>
       <c r="W261">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="262">
@@ -18329,13 +18329,13 @@
         <v>FORM8</v>
       </c>
       <c r="D262">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E262">
         <v>0</v>
       </c>
       <c r="F262">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G262">
         <v>3</v>
@@ -18347,10 +18347,10 @@
         <v>5</v>
       </c>
       <c r="J262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K262">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -18394,40 +18394,40 @@
         <v>AC Form Total</v>
       </c>
       <c r="D263">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="E263">
         <v>0</v>
       </c>
       <c r="F263">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G263">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="H263">
         <v>0</v>
       </c>
       <c r="I263">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J263">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K263">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="L263">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M263">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N263">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O263">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P263">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>230</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S263">
         <v>0</v>
@@ -18451,7 +18451,7 @@
         <v>0</v>
       </c>
       <c r="W263">
-        <v>362</v>
+        <v>378</v>
       </c>
     </row>
     <row r="264">
@@ -18465,25 +18465,25 @@
         <v>FORM6</v>
       </c>
       <c r="D264">
-        <v>4694</v>
+        <v>4720</v>
       </c>
       <c r="E264">
         <v>0</v>
       </c>
       <c r="F264">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G264">
-        <v>1308</v>
+        <v>1333</v>
       </c>
       <c r="H264">
         <v>0</v>
       </c>
       <c r="I264">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J264">
-        <v>709</v>
+        <v>768</v>
       </c>
       <c r="K264">
         <v>0</v>
@@ -18492,10 +18492,10 @@
         <v>0</v>
       </c>
       <c r="M264">
-        <v>2062</v>
+        <v>2015</v>
       </c>
       <c r="N264">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="O264">
         <v>1</v>
@@ -18607,7 +18607,7 @@
         <v>FORM7</v>
       </c>
       <c r="D266">
-        <v>7834</v>
+        <v>7937</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -18616,7 +18616,7 @@
         <v>0</v>
       </c>
       <c r="G266">
-        <v>7039</v>
+        <v>7038</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -18625,16 +18625,16 @@
         <v>0</v>
       </c>
       <c r="J266">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K266">
         <v>1</v>
       </c>
       <c r="L266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M266">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N266">
         <v>0</v>
@@ -18664,7 +18664,7 @@
         <v>0</v>
       </c>
       <c r="W266">
-        <v>423</v>
+        <v>526</v>
       </c>
     </row>
     <row r="267">
@@ -18678,25 +18678,25 @@
         <v>FORM8</v>
       </c>
       <c r="D267">
-        <v>2130</v>
+        <v>2145</v>
       </c>
       <c r="E267">
         <v>0</v>
       </c>
       <c r="F267">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G267">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="H267">
         <v>0</v>
       </c>
       <c r="I267">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J267">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="K267">
         <v>599</v>
@@ -18705,10 +18705,10 @@
         <v>0</v>
       </c>
       <c r="M267">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N267">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O267">
         <v>1</v>
@@ -18743,37 +18743,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D268">
-        <v>14679</v>
+        <v>14823</v>
       </c>
       <c r="E268">
         <v>0</v>
       </c>
       <c r="F268">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="G268">
-        <v>8641</v>
+        <v>8672</v>
       </c>
       <c r="H268">
         <v>0</v>
       </c>
       <c r="I268">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J268">
-        <v>880</v>
+        <v>949</v>
       </c>
       <c r="K268">
         <v>600</v>
       </c>
       <c r="L268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268">
-        <v>2280</v>
+        <v>2230</v>
       </c>
       <c r="N268">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="O268">
         <v>2</v>
@@ -18800,7 +18800,7 @@
         <v>0</v>
       </c>
       <c r="W268">
-        <v>1405</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="269">
@@ -18814,16 +18814,16 @@
         <v>FORM6</v>
       </c>
       <c r="D269">
-        <v>3951</v>
+        <v>4009</v>
       </c>
       <c r="E269">
         <v>0</v>
       </c>
       <c r="F269">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G269">
-        <v>1070</v>
+        <v>983</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -18832,22 +18832,22 @@
         <v>4</v>
       </c>
       <c r="J269">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K269">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="L269">
         <v>14</v>
       </c>
       <c r="M269">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="N269">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P269">
         <v>0</v>
@@ -18856,16 +18856,16 @@
         <v>0</v>
       </c>
       <c r="R269">
-        <v>443</v>
+        <v>508</v>
       </c>
       <c r="S269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T269">
         <v>0</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V269">
         <v>0</v>
@@ -18956,7 +18956,7 @@
         <v>FORM7</v>
       </c>
       <c r="D271">
-        <v>1193</v>
+        <v>1280</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -18965,7 +18965,7 @@
         <v>3</v>
       </c>
       <c r="G271">
-        <v>738</v>
+        <v>666</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -18974,10 +18974,10 @@
         <v>0</v>
       </c>
       <c r="J271">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K271">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="L271">
         <v>5</v>
@@ -19013,7 +19013,7 @@
         <v>0</v>
       </c>
       <c r="W271">
-        <v>145</v>
+        <v>232</v>
       </c>
     </row>
     <row r="272">
@@ -19027,16 +19027,16 @@
         <v>FORM8</v>
       </c>
       <c r="D272">
-        <v>1685</v>
+        <v>1699</v>
       </c>
       <c r="E272">
         <v>0</v>
       </c>
       <c r="F272">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G272">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -19045,10 +19045,10 @@
         <v>1</v>
       </c>
       <c r="J272">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K272">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L272">
         <v>20</v>
@@ -19057,7 +19057,7 @@
         <v>3</v>
       </c>
       <c r="N272">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O272">
         <v>0</v>
@@ -19069,7 +19069,7 @@
         <v>17</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S272">
         <v>0</v>
@@ -19092,16 +19092,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D273">
-        <v>6832</v>
+        <v>6991</v>
       </c>
       <c r="E273">
         <v>0</v>
       </c>
       <c r="F273">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="G273">
-        <v>2031</v>
+        <v>1863</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -19110,22 +19110,22 @@
         <v>5</v>
       </c>
       <c r="J273">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K273">
-        <v>672</v>
+        <v>766</v>
       </c>
       <c r="L273">
         <v>39</v>
       </c>
       <c r="M273">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="N273">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P273">
         <v>0</v>
@@ -19134,22 +19134,22 @@
         <v>225</v>
       </c>
       <c r="R273">
-        <v>443</v>
+        <v>509</v>
       </c>
       <c r="S273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T273">
         <v>0</v>
       </c>
       <c r="U273">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V273">
         <v>0</v>
       </c>
       <c r="W273">
-        <v>2930</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="274">
@@ -19163,37 +19163,37 @@
         <v>FORM6</v>
       </c>
       <c r="D274">
-        <v>2159</v>
+        <v>2173</v>
       </c>
       <c r="E274">
         <v>0</v>
       </c>
       <c r="F274">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G274">
-        <v>854</v>
+        <v>895</v>
       </c>
       <c r="H274">
         <v>0</v>
       </c>
       <c r="I274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J274">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="K274">
-        <v>571</v>
+        <v>628</v>
       </c>
       <c r="L274">
         <v>0</v>
       </c>
       <c r="M274">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="N274">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O274">
         <v>0</v>
@@ -19205,7 +19205,7 @@
         <v>5</v>
       </c>
       <c r="R274">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S274">
         <v>0</v>
@@ -19234,7 +19234,7 @@
         <v>FORM7</v>
       </c>
       <c r="D275">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -19243,7 +19243,7 @@
         <v>0</v>
       </c>
       <c r="G275">
-        <v>1129</v>
+        <v>1063</v>
       </c>
       <c r="H275">
         <v>0</v>
@@ -19252,16 +19252,16 @@
         <v>0</v>
       </c>
       <c r="J275">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="K275">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L275">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M275">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N275">
         <v>0</v>
@@ -19273,10 +19273,10 @@
         <v>0</v>
       </c>
       <c r="Q275">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S275">
         <v>0</v>
@@ -19305,34 +19305,34 @@
         <v>FORM8</v>
       </c>
       <c r="D276">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="E276">
         <v>0</v>
       </c>
       <c r="F276">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G276">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H276">
         <v>0</v>
       </c>
       <c r="I276">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J276">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K276">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="L276">
         <v>0</v>
       </c>
       <c r="M276">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="N276">
         <v>4</v>
@@ -19344,10 +19344,10 @@
         <v>0</v>
       </c>
       <c r="Q276">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R276">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="S276">
         <v>0</v>
@@ -19370,37 +19370,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D277">
-        <v>4791</v>
+        <v>4810</v>
       </c>
       <c r="E277">
         <v>0</v>
       </c>
       <c r="F277">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="G277">
-        <v>2129</v>
+        <v>2106</v>
       </c>
       <c r="H277">
         <v>0</v>
       </c>
       <c r="I277">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J277">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="K277">
-        <v>701</v>
+        <v>839</v>
       </c>
       <c r="L277">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M277">
-        <v>379</v>
+        <v>342</v>
       </c>
       <c r="N277">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O277">
         <v>0</v>
@@ -19409,10 +19409,10 @@
         <v>0</v>
       </c>
       <c r="Q277">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="R277">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="S277">
         <v>0</v>
@@ -19441,16 +19441,16 @@
         <v>FORM6</v>
       </c>
       <c r="D278">
-        <v>2963</v>
+        <v>3000</v>
       </c>
       <c r="E278">
         <v>0</v>
       </c>
       <c r="F278">
-        <v>1283</v>
+        <v>1304</v>
       </c>
       <c r="G278">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -19459,7 +19459,7 @@
         <v>969</v>
       </c>
       <c r="J278">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K278">
         <v>98</v>
@@ -19471,7 +19471,7 @@
         <v>0</v>
       </c>
       <c r="N278">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -19583,7 +19583,7 @@
         <v>FORM7</v>
       </c>
       <c r="D280">
-        <v>6758</v>
+        <v>6759</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -19654,16 +19654,16 @@
         <v>FORM8</v>
       </c>
       <c r="D281">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="E281">
         <v>0</v>
       </c>
       <c r="F281">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G281">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="H281">
         <v>0</v>
@@ -19672,7 +19672,7 @@
         <v>134</v>
       </c>
       <c r="J281">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="K281">
         <v>89</v>
@@ -19719,16 +19719,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D282">
-        <v>10884</v>
+        <v>10935</v>
       </c>
       <c r="E282">
         <v>0</v>
       </c>
       <c r="F282">
-        <v>6901</v>
+        <v>6935</v>
       </c>
       <c r="G282">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="H282">
         <v>0</v>
@@ -19737,7 +19737,7 @@
         <v>1968</v>
       </c>
       <c r="J282">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="K282">
         <v>188</v>
@@ -19749,7 +19749,7 @@
         <v>0</v>
       </c>
       <c r="N282">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O282">
         <v>0</v>
@@ -19776,7 +19776,7 @@
         <v>0</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -19790,25 +19790,25 @@
         <v>FORM6</v>
       </c>
       <c r="D283">
-        <v>3898</v>
+        <v>4079</v>
       </c>
       <c r="E283">
         <v>0</v>
       </c>
       <c r="F283">
-        <v>1777</v>
+        <v>1809</v>
       </c>
       <c r="G283">
-        <v>1425</v>
+        <v>1544</v>
       </c>
       <c r="H283">
         <v>0</v>
       </c>
       <c r="I283">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="J283">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="K283">
         <v>2</v>
@@ -19820,7 +19820,7 @@
         <v>0</v>
       </c>
       <c r="N283">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O283">
         <v>1</v>
@@ -19932,13 +19932,13 @@
         <v>FORM8</v>
       </c>
       <c r="D285">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E285">
         <v>0</v>
       </c>
       <c r="F285">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G285">
         <v>54</v>
@@ -19997,25 +19997,25 @@
         <v>AC Form Total</v>
       </c>
       <c r="D286">
-        <v>10592</v>
+        <v>10775</v>
       </c>
       <c r="E286">
         <v>0</v>
       </c>
       <c r="F286">
-        <v>6636</v>
+        <v>6670</v>
       </c>
       <c r="G286">
-        <v>3168</v>
+        <v>3287</v>
       </c>
       <c r="H286">
         <v>0</v>
       </c>
       <c r="I286">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="J286">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="K286">
         <v>3</v>
@@ -20027,7 +20027,7 @@
         <v>0</v>
       </c>
       <c r="N286">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O286">
         <v>1</v>
@@ -20068,28 +20068,28 @@
         <v>FORM6</v>
       </c>
       <c r="D287">
-        <v>2812</v>
+        <v>2831</v>
       </c>
       <c r="E287">
         <v>0</v>
       </c>
       <c r="F287">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="G287">
-        <v>1814</v>
+        <v>1825</v>
       </c>
       <c r="H287">
         <v>0</v>
       </c>
       <c r="I287">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J287">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="K287">
-        <v>642</v>
+        <v>676</v>
       </c>
       <c r="L287">
         <v>0</v>
@@ -20098,7 +20098,7 @@
         <v>0</v>
       </c>
       <c r="N287">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O287">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>FORM7</v>
       </c>
       <c r="D289">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -20228,10 +20228,10 @@
         <v>0</v>
       </c>
       <c r="J289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K289">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L289">
         <v>399</v>
@@ -20267,7 +20267,7 @@
         <v>0</v>
       </c>
       <c r="W289">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290">
@@ -20281,28 +20281,28 @@
         <v>FORM8</v>
       </c>
       <c r="D290">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="E290">
         <v>0</v>
       </c>
       <c r="F290">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G290">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I290">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J290">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K290">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="L290">
         <v>0</v>
@@ -20311,7 +20311,7 @@
         <v>0</v>
       </c>
       <c r="N290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O290">
         <v>0</v>
@@ -20346,28 +20346,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D291">
-        <v>6058</v>
+        <v>6088</v>
       </c>
       <c r="E291">
         <v>0</v>
       </c>
       <c r="F291">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="G291">
-        <v>3690</v>
+        <v>3706</v>
       </c>
       <c r="H291">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I291">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J291">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="K291">
-        <v>1024</v>
+        <v>1077</v>
       </c>
       <c r="L291">
         <v>399</v>
@@ -20376,7 +20376,7 @@
         <v>0</v>
       </c>
       <c r="N291">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O291">
         <v>0</v>
@@ -20403,7 +20403,7 @@
         <v>0</v>
       </c>
       <c r="W291">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="292">
@@ -20417,13 +20417,13 @@
         <v>FORM6</v>
       </c>
       <c r="D292">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E292">
         <v>0</v>
       </c>
       <c r="F292">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G292">
         <v>140</v>
@@ -20488,7 +20488,7 @@
         <v>FORM7</v>
       </c>
       <c r="D293">
-        <v>4873</v>
+        <v>5166</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -20527,7 +20527,7 @@
         <v>0</v>
       </c>
       <c r="Q293">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="R293">
         <v>0</v>
@@ -20559,13 +20559,13 @@
         <v>FORM8</v>
       </c>
       <c r="D294">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="E294">
         <v>0</v>
       </c>
       <c r="F294">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G294">
         <v>72</v>
@@ -20624,13 +20624,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D295">
-        <v>6582</v>
+        <v>6890</v>
       </c>
       <c r="E295">
         <v>0</v>
       </c>
       <c r="F295">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="G295">
         <v>4986</v>
@@ -20663,7 +20663,7 @@
         <v>0</v>
       </c>
       <c r="Q295">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="R295">
         <v>2</v>
@@ -20695,22 +20695,22 @@
         <v>FORM6</v>
       </c>
       <c r="D296">
-        <v>2356</v>
+        <v>2530</v>
       </c>
       <c r="E296">
         <v>0</v>
       </c>
       <c r="F296">
-        <v>280</v>
+        <v>133</v>
       </c>
       <c r="G296">
-        <v>1762</v>
+        <v>2054</v>
       </c>
       <c r="H296">
         <v>0</v>
       </c>
       <c r="I296">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="J296">
         <v>5</v>
@@ -20725,7 +20725,7 @@
         <v>0</v>
       </c>
       <c r="N296">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O296">
         <v>1</v>
@@ -20772,10 +20772,10 @@
         <v>0</v>
       </c>
       <c r="F297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -20908,25 +20908,25 @@
         <v>FORM8</v>
       </c>
       <c r="D299">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="E299">
         <v>0</v>
       </c>
       <c r="F299">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G299">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H299">
         <v>0</v>
       </c>
       <c r="I299">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J299">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K299">
         <v>0</v>
@@ -20973,25 +20973,25 @@
         <v>AC Form Total</v>
       </c>
       <c r="D300">
-        <v>9408</v>
+        <v>9588</v>
       </c>
       <c r="E300">
         <v>0</v>
       </c>
       <c r="F300">
-        <v>458</v>
+        <v>311</v>
       </c>
       <c r="G300">
-        <v>7577</v>
+        <v>7871</v>
       </c>
       <c r="H300">
         <v>0</v>
       </c>
       <c r="I300">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="J300">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K300">
         <v>815</v>
@@ -21003,7 +21003,7 @@
         <v>0</v>
       </c>
       <c r="N300">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O300">
         <v>1</v>
@@ -21044,16 +21044,16 @@
         <v>FORM6</v>
       </c>
       <c r="D301">
-        <v>1347</v>
+        <v>1364</v>
       </c>
       <c r="E301">
         <v>0</v>
       </c>
       <c r="F301">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G301">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -21062,7 +21062,7 @@
         <v>15</v>
       </c>
       <c r="J301">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K301">
         <v>1</v>
@@ -21074,7 +21074,7 @@
         <v>14</v>
       </c>
       <c r="N301">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O301">
         <v>4</v>
@@ -21124,7 +21124,7 @@
         <v>6412</v>
       </c>
       <c r="G302">
-        <v>1568</v>
+        <v>1315</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>1</v>
       </c>
       <c r="J302">
-        <v>139</v>
+        <v>403</v>
       </c>
       <c r="K302">
         <v>2068</v>
@@ -21142,7 +21142,7 @@
         <v>2</v>
       </c>
       <c r="M302">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="N302">
         <v>0</v>
@@ -21186,16 +21186,16 @@
         <v>FORM8</v>
       </c>
       <c r="D303">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="E303">
         <v>0</v>
       </c>
       <c r="F303">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G303">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H303">
         <v>0</v>
@@ -21204,7 +21204,7 @@
         <v>65</v>
       </c>
       <c r="J303">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="K303">
         <v>80</v>
@@ -21251,16 +21251,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D304">
-        <v>13022</v>
+        <v>13050</v>
       </c>
       <c r="E304">
         <v>0</v>
       </c>
       <c r="F304">
-        <v>6570</v>
+        <v>6595</v>
       </c>
       <c r="G304">
-        <v>3058</v>
+        <v>2795</v>
       </c>
       <c r="H304">
         <v>0</v>
@@ -21269,7 +21269,7 @@
         <v>81</v>
       </c>
       <c r="J304">
-        <v>559</v>
+        <v>835</v>
       </c>
       <c r="K304">
         <v>2149</v>
@@ -21278,10 +21278,10 @@
         <v>2</v>
       </c>
       <c r="M304">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="N304">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O304">
         <v>4</v>
@@ -21322,16 +21322,16 @@
         <v>FORM6</v>
       </c>
       <c r="D305">
-        <v>1925</v>
+        <v>1997</v>
       </c>
       <c r="E305">
         <v>0</v>
       </c>
       <c r="F305">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G305">
-        <v>1665</v>
+        <v>1418</v>
       </c>
       <c r="H305">
         <v>1</v>
@@ -21340,7 +21340,7 @@
         <v>21</v>
       </c>
       <c r="J305">
-        <v>62</v>
+        <v>352</v>
       </c>
       <c r="K305">
         <v>2</v>
@@ -21464,13 +21464,13 @@
         <v>FORM8</v>
       </c>
       <c r="D307">
-        <v>939</v>
+        <v>956</v>
       </c>
       <c r="E307">
         <v>0</v>
       </c>
       <c r="F307">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G307">
         <v>663</v>
@@ -21482,7 +21482,7 @@
         <v>29</v>
       </c>
       <c r="J307">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K307">
         <v>0</v>
@@ -21529,16 +21529,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D308">
-        <v>4558</v>
+        <v>4647</v>
       </c>
       <c r="E308">
         <v>0</v>
       </c>
       <c r="F308">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="G308">
-        <v>3392</v>
+        <v>3145</v>
       </c>
       <c r="H308">
         <v>1</v>
@@ -21547,7 +21547,7 @@
         <v>51</v>
       </c>
       <c r="J308">
-        <v>744</v>
+        <v>1038</v>
       </c>
       <c r="K308">
         <v>115</v>
@@ -21600,16 +21600,16 @@
         <v>FORM6</v>
       </c>
       <c r="D309">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="E309">
         <v>0</v>
       </c>
       <c r="F309">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G309">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -21618,7 +21618,7 @@
         <v>0</v>
       </c>
       <c r="J309">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K309">
         <v>1</v>
@@ -21630,10 +21630,10 @@
         <v>0</v>
       </c>
       <c r="N309">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P309">
         <v>0</v>
@@ -21742,16 +21742,16 @@
         <v>FORM8</v>
       </c>
       <c r="D311">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="E311">
         <v>0</v>
       </c>
       <c r="F311">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G311">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="H311">
         <v>0</v>
@@ -21760,7 +21760,7 @@
         <v>31</v>
       </c>
       <c r="J311">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="K311">
         <v>0</v>
@@ -21775,7 +21775,7 @@
         <v>47</v>
       </c>
       <c r="O311">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P311">
         <v>0</v>
@@ -21807,16 +21807,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D312">
-        <v>3790</v>
+        <v>3813</v>
       </c>
       <c r="E312">
         <v>0</v>
       </c>
       <c r="F312">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G312">
-        <v>2428</v>
+        <v>2415</v>
       </c>
       <c r="H312">
         <v>0</v>
@@ -21825,7 +21825,7 @@
         <v>31</v>
       </c>
       <c r="J312">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="K312">
         <v>1</v>
@@ -21837,10 +21837,10 @@
         <v>0</v>
       </c>
       <c r="N312">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O312">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P312">
         <v>0</v>
@@ -21878,40 +21878,40 @@
         <v>FORM6</v>
       </c>
       <c r="D313">
-        <v>1020</v>
+        <v>1055</v>
       </c>
       <c r="E313">
         <v>0</v>
       </c>
       <c r="F313">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G313">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H313">
         <v>0</v>
       </c>
       <c r="I313">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J313">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K313">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="L313">
         <v>0</v>
       </c>
       <c r="M313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N313">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="O313">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P313">
         <v>0</v>
@@ -21920,7 +21920,7 @@
         <v>1</v>
       </c>
       <c r="R313">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S313">
         <v>0</v>
@@ -22091,25 +22091,25 @@
         <v>FORM8</v>
       </c>
       <c r="D316">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E316">
         <v>0</v>
       </c>
       <c r="F316">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G316">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="H316">
         <v>0</v>
       </c>
       <c r="I316">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J316">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="K316">
         <v>0</v>
@@ -22121,7 +22121,7 @@
         <v>0</v>
       </c>
       <c r="N316">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O316">
         <v>0</v>
@@ -22130,7 +22130,7 @@
         <v>0</v>
       </c>
       <c r="Q316">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R316">
         <v>0</v>
@@ -22156,49 +22156,49 @@
         <v>AC Form Total</v>
       </c>
       <c r="D317">
-        <v>2655</v>
+        <v>2693</v>
       </c>
       <c r="E317">
         <v>0</v>
       </c>
       <c r="F317">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="G317">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="H317">
         <v>0</v>
       </c>
       <c r="I317">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J317">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="K317">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="L317">
         <v>0</v>
       </c>
       <c r="M317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N317">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="O317">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P317">
         <v>0</v>
       </c>
       <c r="Q317">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R317">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S317">
         <v>0</v>
@@ -22221,58 +22221,58 @@
         <v>All AC Form-6 Total</v>
       </c>
       <c r="D318">
-        <v>141788</v>
+        <v>143485</v>
       </c>
       <c r="E318">
         <v>0</v>
       </c>
       <c r="F318">
-        <v>9447</v>
+        <v>9454</v>
       </c>
       <c r="G318">
-        <v>39368</v>
+        <v>37301</v>
       </c>
       <c r="H318">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I318">
-        <v>5570</v>
+        <v>4828</v>
       </c>
       <c r="J318">
-        <v>13518</v>
+        <v>13215</v>
       </c>
       <c r="K318">
-        <v>36440</v>
+        <v>37951</v>
       </c>
       <c r="L318">
-        <v>4501</v>
+        <v>4668</v>
       </c>
       <c r="M318">
-        <v>4213</v>
+        <v>4434</v>
       </c>
       <c r="N318">
-        <v>2584</v>
+        <v>3416</v>
       </c>
       <c r="O318">
-        <v>828</v>
+        <v>740</v>
       </c>
       <c r="P318">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q318">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="R318">
-        <v>3897</v>
+        <v>6026</v>
       </c>
       <c r="S318">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T318">
         <v>0</v>
       </c>
       <c r="U318">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="V318">
         <v>0</v>
@@ -22292,7 +22292,7 @@
         <v>0</v>
       </c>
       <c r="F319">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G319">
         <v>8</v>
@@ -22304,7 +22304,7 @@
         <v>12</v>
       </c>
       <c r="J319">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K319">
         <v>4</v>
@@ -22351,34 +22351,34 @@
         <v>All AC Form-7 Total</v>
       </c>
       <c r="D320">
-        <v>95320</v>
+        <v>96056</v>
       </c>
       <c r="E320">
         <v>0</v>
       </c>
       <c r="F320">
-        <v>17129</v>
+        <v>17108</v>
       </c>
       <c r="G320">
-        <v>34584</v>
+        <v>33255</v>
       </c>
       <c r="H320">
         <v>0</v>
       </c>
       <c r="I320">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="J320">
-        <v>2193</v>
+        <v>2565</v>
       </c>
       <c r="K320">
-        <v>7611</v>
+        <v>6747</v>
       </c>
       <c r="L320">
-        <v>13679</v>
+        <v>15513</v>
       </c>
       <c r="M320">
-        <v>760</v>
+        <v>745</v>
       </c>
       <c r="N320">
         <v>0</v>
@@ -22390,10 +22390,10 @@
         <v>0</v>
       </c>
       <c r="Q320">
-        <v>14761</v>
+        <v>15133</v>
       </c>
       <c r="R320">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="S320">
         <v>0</v>
@@ -22408,7 +22408,7 @@
         <v>0</v>
       </c>
       <c r="W320">
-        <v>3211</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="321">
@@ -22416,49 +22416,49 @@
         <v>All AC Form-8 Total</v>
       </c>
       <c r="D321">
-        <v>50404</v>
+        <v>50936</v>
       </c>
       <c r="E321">
         <v>0</v>
       </c>
       <c r="F321">
-        <v>6625</v>
+        <v>6201</v>
       </c>
       <c r="G321">
-        <v>7738</v>
+        <v>7372</v>
       </c>
       <c r="H321">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I321">
-        <v>4476</v>
+        <v>4872</v>
       </c>
       <c r="J321">
-        <v>4311</v>
+        <v>4084</v>
       </c>
       <c r="K321">
-        <v>8148</v>
+        <v>8550</v>
       </c>
       <c r="L321">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="M321">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="N321">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="O321">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="P321">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q321">
-        <v>675</v>
+        <v>759</v>
       </c>
       <c r="R321">
-        <v>4286</v>
+        <v>4942</v>
       </c>
       <c r="S321">
         <v>1</v>
@@ -22473,7 +22473,7 @@
         <v>0</v>
       </c>
       <c r="W321">
-        <v>13177</v>
+        <v>13180</v>
       </c>
     </row>
     <row r="322">
@@ -22481,64 +22481,64 @@
         <v>All AC Form Total</v>
       </c>
       <c r="D322">
-        <v>287612</v>
+        <v>290577</v>
       </c>
       <c r="E322">
         <v>0</v>
       </c>
       <c r="F322">
-        <v>33245</v>
+        <v>32806</v>
       </c>
       <c r="G322">
-        <v>81698</v>
+        <v>77936</v>
       </c>
       <c r="H322">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I322">
-        <v>11384</v>
+        <v>11042</v>
       </c>
       <c r="J322">
-        <v>20043</v>
+        <v>19886</v>
       </c>
       <c r="K322">
-        <v>52203</v>
+        <v>53252</v>
       </c>
       <c r="L322">
-        <v>18485</v>
+        <v>20505</v>
       </c>
       <c r="M322">
-        <v>5307</v>
+        <v>5484</v>
       </c>
       <c r="N322">
-        <v>2807</v>
+        <v>3649</v>
       </c>
       <c r="O322">
-        <v>855</v>
+        <v>777</v>
       </c>
       <c r="P322">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q322">
-        <v>16290</v>
+        <v>16778</v>
       </c>
       <c r="R322">
-        <v>8241</v>
+        <v>11039</v>
       </c>
       <c r="S322">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T322">
         <v>0</v>
       </c>
       <c r="U322">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="V322">
         <v>0</v>
       </c>
       <c r="W322">
-        <v>36910</v>
+        <v>37283</v>
       </c>
     </row>
   </sheetData>
